--- a/data/trans_bre/P16A07-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A07-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,02</t>
+          <t>0,61; 3,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,25</t>
+          <t>-0,8; 1,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,24</t>
+          <t>-0,74; 1,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,57</t>
+          <t>0,14; 5,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,7</t>
+          <t>0,42; 3,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,68</t>
+          <t>-0,06; 3,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,53</t>
+          <t>-0,2; 2,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,17</t>
+          <t>0,58; 4,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,9; 524,63</t>
+          <t>9,58; 496,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 410,83</t>
+          <t>-18,66; 393,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 584,17</t>
+          <t>-27,46; 578,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 6593,3</t>
+          <t>5,38; 7269,2</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,5</t>
+          <t>-0,31; 3,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,24</t>
+          <t>2,38; 7,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,92</t>
+          <t>0,45; 4,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,94</t>
+          <t>-0,27; 3,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 261,91</t>
+          <t>-14,06; 251,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,43; 331,03</t>
+          <t>49,34; 347,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 292,91</t>
+          <t>9,67; 346,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 252,73</t>
+          <t>-11,74; 244,63</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 9,4</t>
+          <t>3,91; 9,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,98</t>
+          <t>3,22; 8,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,77</t>
+          <t>3,6; 8,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 7,42</t>
+          <t>1,26; 7,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>100,78; 757,99</t>
+          <t>109,13; 772,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,12; 408,48</t>
+          <t>67,58; 377,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,46; 518,67</t>
+          <t>97,34; 490,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,91; 418,85</t>
+          <t>19,86; 385,27</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,18; 12,78</t>
+          <t>5,1; 12,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 14,19</t>
+          <t>5,81; 14,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 10,83</t>
+          <t>3,42; 10,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 9,54</t>
+          <t>4,2; 9,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>99,05; 503,6</t>
+          <t>101,35; 590,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,83; 326,87</t>
+          <t>74,04; 372,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,0; 408,94</t>
+          <t>51,32; 374,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,27; 215,89</t>
+          <t>55,16; 220,44</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 10,41</t>
+          <t>2,93; 10,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,3; 13,26</t>
+          <t>4,28; 13,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,15; 15,82</t>
+          <t>7,53; 15,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 10,48</t>
+          <t>0,08; 10,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45,27; 481,71</t>
+          <t>41,24; 460,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,81; 518,55</t>
+          <t>63,49; 519,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>228,5; 1641,8</t>
+          <t>219,35; 1715,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,44; 575,92</t>
+          <t>-0,05; 521,3</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 9,57</t>
+          <t>0,32; 9,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,75</t>
+          <t>1,03; 10,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,58; 12,3</t>
+          <t>3,34; 12,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,79</t>
+          <t>0,93; 7,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 358,91</t>
+          <t>1,07; 385,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,72; 324,29</t>
+          <t>7,49; 329,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,88; 498,9</t>
+          <t>49,95; 501,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,36; 159,77</t>
+          <t>10,74; 164,99</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,34</t>
+          <t>3,38; 5,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,26</t>
+          <t>4,08; 6,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,94</t>
+          <t>3,92; 6,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,04</t>
+          <t>2,51; 5,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>130,75; 301,93</t>
+          <t>131,42; 291,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>107,3; 230,64</t>
+          <t>109,6; 236,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>155,29; 331,8</t>
+          <t>147,97; 327,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>65,87; 187,79</t>
+          <t>73,01; 191,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A07-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A07-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>514,05%</t>
+          <t>196,5%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,07</t>
+          <t>0,61; 3,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,21</t>
+          <t>-0,83; 1,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,43</t>
+          <t>-0,72; 1,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,47</t>
+          <t>-0,5; 4,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>399,27%</t>
+          <t>225,32%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,67</t>
+          <t>0,4; 3,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 3,52</t>
+          <t>-0,2; 3,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,68</t>
+          <t>-0,17; 2,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,18</t>
+          <t>0,29; 3,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 496,5</t>
+          <t>9,88; 512,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 393,14</t>
+          <t>-14,73; 398,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 578,52</t>
+          <t>-30,56; 568,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7269,2</t>
+          <t>-9,28; 1444,21</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>2,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,51</t>
+          <t>-0,26; 3,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,36</t>
+          <t>2,07; 7,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,3</t>
+          <t>0,42; 3,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,93</t>
+          <t>-0,04; 3,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 251,85</t>
+          <t>-13,14; 237,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,34; 347,0</t>
+          <t>40,64; 365,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,67; 346,77</t>
+          <t>10,47; 301,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 244,63</t>
+          <t>-7,16; 276,66</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,99</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>101,52%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 9,55</t>
+          <t>3,75; 9,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,75</t>
+          <t>3,04; 8,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 8,75</t>
+          <t>3,7; 8,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,41</t>
+          <t>0,26; 5,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>109,13; 772,9</t>
+          <t>92,53; 704,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,58; 377,14</t>
+          <t>61,37; 368,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,34; 490,88</t>
+          <t>101,99; 547,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,86; 385,27</t>
+          <t>3,97; 141,65</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,82</t>
+          <t>6,97</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>116,55%</t>
+          <t>123,55%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 12,8</t>
+          <t>5,32; 13,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 14,34</t>
+          <t>6,18; 14,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 10,62</t>
+          <t>3,95; 10,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 9,78</t>
+          <t>4,21; 9,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>101,35; 590,45</t>
+          <t>102,13; 545,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,04; 372,2</t>
+          <t>73,99; 332,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,32; 374,82</t>
+          <t>69,74; 396,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>55,16; 220,44</t>
+          <t>56,35; 224,08</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>9,56</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>232,27%</t>
+          <t>407,16%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 10,52</t>
+          <t>2,22; 9,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,28; 13,08</t>
+          <t>3,92; 12,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 15,33</t>
+          <t>8,01; 15,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 10,63</t>
+          <t>7,15; 12,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,24; 460,88</t>
+          <t>40,25; 431,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63,49; 519,46</t>
+          <t>54,38; 506,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>219,35; 1715,11</t>
+          <t>233,22; 1450,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 521,3</t>
+          <t>186,98; 858,82</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>3,99</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 9,6</t>
+          <t>0,39; 9,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 10,22</t>
+          <t>1,09; 10,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,34; 12,22</t>
+          <t>3,71; 12,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,22</t>
+          <t>0,49; 6,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 385,47</t>
+          <t>-0,51; 363,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,49; 329,67</t>
+          <t>10,26; 303,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,95; 501,64</t>
+          <t>53,29; 464,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,74; 164,99</t>
+          <t>4,41; 154,5</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,94</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>121,83%</t>
+          <t>122,45%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,25</t>
+          <t>3,29; 5,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 6,39</t>
+          <t>4,01; 6,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,09</t>
+          <t>3,9; 5,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,12</t>
+          <t>3,26; 5,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>131,42; 291,01</t>
+          <t>125,11; 288,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>109,6; 236,2</t>
+          <t>109,06; 236,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>147,97; 327,52</t>
+          <t>151,89; 324,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>73,01; 191,07</t>
+          <t>81,58; 168,06</t>
         </is>
       </c>
     </row>
